--- a/dy_memo/요청데이터_20251010/INOPNC_샘플데이터.xlsx
+++ b/dy_memo/요청데이터_20251010/INOPNC_샘플데이터.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inopn\OneDrive\바탕 화면\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidyang/workspace/INOPNC_WM_20250829/dy_memo/요청데이터_20251010/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B643713B-AB97-4B4D-ABB4-3DC30B09CB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5340767F-FD0C-D740-8836-E8D94F8D7E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="921" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="500" windowWidth="29040" windowHeight="26220" tabRatio="921" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_소속사" sheetId="1" r:id="rId1"/>
@@ -2448,7 +2448,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2834,13 +2834,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B61"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>636</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>636</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>763</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>770</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>772</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>772</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>736</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>736</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>736</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>736</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>765</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>736</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>736</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>736</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>736</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>736</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>738</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>718</v>
       </c>
@@ -2992,12 +2992,12 @@
         <v>774</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>736</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>736</v>
       </c>
@@ -3013,12 +3013,12 @@
         <v>771</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>736</v>
       </c>
@@ -3026,12 +3026,12 @@
         <v>771</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>736</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>736</v>
       </c>
@@ -3047,12 +3047,12 @@
         <v>771</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>736</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>768</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>736</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>718</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>736</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>736</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>736</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>746</v>
       </c>
@@ -3116,12 +3116,12 @@
         <v>775</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>736</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>736</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>736</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>736</v>
       </c>
@@ -3153,12 +3153,12 @@
         <v>771</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>736</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>736</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>636</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>738</v>
       </c>
@@ -3190,17 +3190,17 @@
         <v>778</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>736</v>
       </c>
@@ -3208,12 +3208,12 @@
         <v>771</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>736</v>
       </c>
@@ -3221,12 +3221,12 @@
         <v>771</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>736</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>736</v>
       </c>
@@ -3242,12 +3242,12 @@
         <v>771</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>736</v>
       </c>
@@ -3255,12 +3255,12 @@
         <v>771</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>636</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>636</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>736</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>736</v>
       </c>
@@ -3301,13 +3301,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C61"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="2" max="2" width="17.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -3483,7 +3483,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>46</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>52</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>60</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>62</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>64</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>70</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>78</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>80</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="B41" s="4" t="s">
         <v>736</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="B42" s="4" t="s">
         <v>741</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="B43" s="4" t="s">
         <v>736</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="B44" s="4" t="s">
         <v>736</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="B45" s="4" t="s">
         <v>636</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="B46" s="4" t="s">
         <v>738</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="B47" s="4" t="s">
         <v>736</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="B48" s="4" t="s">
         <v>751</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:3">
       <c r="B49" s="4" t="s">
         <v>736</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:3">
       <c r="B50" s="4" t="s">
         <v>741</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:3">
       <c r="B51" s="4" t="s">
         <v>736</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:3">
       <c r="B52" s="4" t="s">
         <v>738</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:3">
       <c r="B53" s="4" t="s">
         <v>736</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:3">
       <c r="B54" s="4" t="s">
         <v>736</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:3">
       <c r="B55" s="4" t="s">
         <v>741</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:3">
       <c r="B56" s="4" t="s">
         <v>736</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:3">
       <c r="B57" s="4" t="s">
         <v>738</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:3">
       <c r="B58" s="4" t="s">
         <v>636</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:3">
       <c r="B59" s="4" t="s">
         <v>636</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:3">
       <c r="B60" s="4" t="s">
         <v>736</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:3">
       <c r="B61" s="4" t="s">
         <v>736</v>
       </c>
@@ -3924,15 +3924,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F196"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.1640625" customWidth="1"/>
+    <col min="6" max="6" width="45.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>112</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>117</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>119</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>121</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>123</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>125</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>127</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>129</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>131</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>137</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>139</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>141</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>143</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>145</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>147</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>149</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>151</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>153</v>
       </c>
@@ -4332,7 +4332,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>155</v>
       </c>
@@ -4352,7 +4352,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>157</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>159</v>
       </c>
@@ -4392,7 +4392,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>161</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>163</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>165</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>167</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>169</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>171</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>173</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>175</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>177</v>
       </c>
@@ -4572,7 +4572,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>179</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>181</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>183</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>187</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>189</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>191</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>193</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>195</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>197</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>199</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>201</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>203</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>205</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>207</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>209</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>211</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>213</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>215</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>217</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>219</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>221</v>
       </c>
@@ -5012,7 +5012,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>223</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>225</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>227</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>229</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>231</v>
       </c>
@@ -5112,7 +5112,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>233</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>235</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>237</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>239</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>241</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>243</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>245</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>247</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>249</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>251</v>
       </c>
@@ -5312,7 +5312,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>253</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>255</v>
       </c>
@@ -5352,7 +5352,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>257</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>259</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>261</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>263</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>265</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>267</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>269</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>271</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>273</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>275</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>277</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>279</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>281</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>283</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>285</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>287</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>289</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>291</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>293</v>
       </c>
@@ -5732,7 +5732,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>295</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>297</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>299</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>301</v>
       </c>
@@ -5812,7 +5812,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>303</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>305</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>307</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>309</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>311</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>313</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>315</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>317</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>319</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>321</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>323</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>325</v>
       </c>
@@ -6052,7 +6052,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>327</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>329</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>331</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>333</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>335</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>337</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>339</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>341</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>343</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>345</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>347</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>349</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>351</v>
       </c>
@@ -6312,7 +6312,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>353</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>355</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>357</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>359</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>361</v>
       </c>
@@ -6412,7 +6412,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>363</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>365</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>367</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>369</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>371</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>373</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>375</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>377</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>379</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>381</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
         <v>383</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
         <v>385</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
         <v>387</v>
       </c>
@@ -6672,7 +6672,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>389</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>391</v>
       </c>
@@ -6712,7 +6712,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>393</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>395</v>
       </c>
@@ -6752,7 +6752,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>397</v>
       </c>
@@ -6772,7 +6772,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>399</v>
       </c>
@@ -6792,7 +6792,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
         <v>401</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>403</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>405</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
         <v>407</v>
       </c>
@@ -6872,7 +6872,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
         <v>409</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
         <v>411</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
         <v>413</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
         <v>415</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
         <v>417</v>
       </c>
@@ -6972,7 +6972,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
         <v>419</v>
       </c>
@@ -6992,7 +6992,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
         <v>421</v>
       </c>
@@ -7012,7 +7012,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
         <v>423</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
         <v>425</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
         <v>427</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
         <v>429</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
         <v>431</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
         <v>433</v>
       </c>
@@ -7132,7 +7132,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
         <v>435</v>
       </c>
@@ -7152,7 +7152,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
         <v>437</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6">
       <c r="A163" t="s">
         <v>439</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
         <v>441</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6">
       <c r="A165" t="s">
         <v>443</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
         <v>445</v>
       </c>
@@ -7252,7 +7252,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
         <v>447</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
         <v>449</v>
       </c>
@@ -7292,7 +7292,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6">
       <c r="A169" t="s">
         <v>451</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
         <v>453</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6">
       <c r="A171" t="s">
         <v>455</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6">
       <c r="A172" t="s">
         <v>457</v>
       </c>
@@ -7372,7 +7372,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
         <v>459</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
         <v>461</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
         <v>463</v>
       </c>
@@ -7432,7 +7432,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
         <v>465</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>467</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6">
       <c r="A178" t="s">
         <v>469</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>471</v>
       </c>
@@ -7512,7 +7512,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>473</v>
       </c>
@@ -7532,7 +7532,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>475</v>
       </c>
@@ -7552,7 +7552,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>477</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
         <v>479</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6">
       <c r="A184" t="s">
         <v>481</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6">
       <c r="A185" t="s">
         <v>483</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6">
       <c r="A186" t="s">
         <v>485</v>
       </c>
@@ -7652,7 +7652,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6">
       <c r="A187" t="s">
         <v>487</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6">
       <c r="A188" t="s">
         <v>489</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6">
       <c r="A189" t="s">
         <v>491</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6">
       <c r="A190" t="s">
         <v>493</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6">
       <c r="A191" t="s">
         <v>495</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6">
       <c r="A192" t="s">
         <v>497</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>499</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6">
       <c r="A194" t="s">
         <v>501</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>503</v>
       </c>
@@ -7832,7 +7832,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>505</v>
       </c>
@@ -7861,12 +7861,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>88</v>
       </c>
@@ -7909,7 +7909,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>92</v>
       </c>
@@ -7926,7 +7926,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>94</v>
       </c>
@@ -7943,7 +7943,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>98</v>
       </c>
@@ -7977,7 +7977,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>100</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -8011,7 +8011,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>104</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>106</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>108</v>
       </c>
@@ -8062,7 +8062,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>110</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>785</v>
       </c>
@@ -8090,7 +8090,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>786</v>
       </c>
@@ -8101,7 +8101,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>787</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>788</v>
       </c>
@@ -8123,7 +8123,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>789</v>
       </c>
@@ -8134,7 +8134,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>790</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>793</v>
       </c>
@@ -8156,7 +8156,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>794</v>
       </c>
@@ -8176,13 +8176,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>508</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>513</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>517</v>
       </c>
@@ -8239,7 +8239,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>519</v>
       </c>
@@ -8256,7 +8256,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>521</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>523</v>
       </c>
@@ -8290,7 +8290,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>525</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>527</v>
       </c>
@@ -8324,7 +8324,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>529</v>
       </c>
@@ -8341,7 +8341,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>531</v>
       </c>
@@ -8358,7 +8358,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>533</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>535</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>537</v>
       </c>
@@ -8409,7 +8409,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>539</v>
       </c>
@@ -8426,7 +8426,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>541</v>
       </c>
@@ -8443,7 +8443,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>543</v>
       </c>
@@ -8460,7 +8460,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>545</v>
       </c>
@@ -8477,7 +8477,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>547</v>
       </c>
@@ -8494,7 +8494,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>549</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>551</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>553</v>
       </c>
@@ -8545,7 +8545,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>555</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>557</v>
       </c>
@@ -8579,7 +8579,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>559</v>
       </c>
@@ -8596,7 +8596,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>561</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>563</v>
       </c>
@@ -8630,7 +8630,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>565</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>567</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>569</v>
       </c>
@@ -8681,7 +8681,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>571</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>573</v>
       </c>
@@ -8715,7 +8715,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>575</v>
       </c>
@@ -8732,7 +8732,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>577</v>
       </c>
@@ -8749,7 +8749,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>579</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>581</v>
       </c>
@@ -8783,7 +8783,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>583</v>
       </c>
@@ -8800,7 +8800,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>585</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>587</v>
       </c>
@@ -8834,7 +8834,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>589</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>591</v>
       </c>
@@ -8877,14 +8877,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:I450"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="11.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="47.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="47.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>593</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="A2" s="6">
         <v>45659</v>
       </c>
@@ -8939,7 +8939,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" s="6">
         <v>45659</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" s="6">
         <v>45659</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" s="6">
         <v>45659</v>
       </c>
@@ -9017,7 +9017,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" s="6">
         <v>45659</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" s="6">
         <v>45660</v>
       </c>
@@ -9069,7 +9069,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" s="6">
         <v>45660</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" s="6">
         <v>45660</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" s="6">
         <v>45660</v>
       </c>
@@ -9147,7 +9147,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" s="6">
         <v>45660</v>
       </c>
@@ -9173,7 +9173,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12" s="6">
         <v>45660</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" s="6">
         <v>45661</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14" s="6">
         <v>45661</v>
       </c>
@@ -9251,7 +9251,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" s="6">
         <v>45661</v>
       </c>
@@ -9277,7 +9277,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" s="6">
         <v>45663</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8">
       <c r="A17" s="6">
         <v>45663</v>
       </c>
@@ -9329,7 +9329,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18" s="6">
         <v>45663</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8">
       <c r="A19" s="6">
         <v>45664</v>
       </c>
@@ -9381,7 +9381,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20" s="6">
         <v>45664</v>
       </c>
@@ -9407,7 +9407,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8">
       <c r="A21" s="6">
         <v>45664</v>
       </c>
@@ -9433,7 +9433,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8">
       <c r="A22" s="6">
         <v>45664</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8">
       <c r="A23" s="6">
         <v>45664</v>
       </c>
@@ -9485,7 +9485,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8">
       <c r="A24" s="6">
         <v>45665</v>
       </c>
@@ -9511,7 +9511,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8">
       <c r="A25" s="6">
         <v>45665</v>
       </c>
@@ -9537,7 +9537,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26" s="6">
         <v>45665</v>
       </c>
@@ -9563,7 +9563,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27" s="6">
         <v>45665</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28" s="6">
         <v>45665</v>
       </c>
@@ -9615,7 +9615,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29" s="6">
         <v>45666</v>
       </c>
@@ -9641,7 +9641,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30" s="6">
         <v>45666</v>
       </c>
@@ -9667,7 +9667,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31" s="6">
         <v>45666</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32" s="6">
         <v>45666</v>
       </c>
@@ -9719,7 +9719,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33" s="6">
         <v>45666</v>
       </c>
@@ -9745,7 +9745,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8">
       <c r="A34" s="6">
         <v>45667</v>
       </c>
@@ -9771,7 +9771,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="A35" s="6">
         <v>45667</v>
       </c>
@@ -9797,7 +9797,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36" s="6">
         <v>45667</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8">
       <c r="A37" s="6">
         <v>45667</v>
       </c>
@@ -9849,7 +9849,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38" s="6">
         <v>45667</v>
       </c>
@@ -9875,7 +9875,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39" s="6">
         <v>45667</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="A40" s="6">
         <v>45668</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="A41" s="6">
         <v>45668</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="A42" s="6">
         <v>45668</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="A43" s="6">
         <v>45670</v>
       </c>
@@ -10005,7 +10005,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8">
       <c r="A44" s="6">
         <v>45670</v>
       </c>
@@ -10031,7 +10031,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8">
       <c r="A45" s="6">
         <v>45670</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8">
       <c r="A46" s="6">
         <v>45670</v>
       </c>
@@ -10083,7 +10083,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8">
       <c r="A47" s="6">
         <v>45670</v>
       </c>
@@ -10109,7 +10109,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8">
       <c r="A48" s="6">
         <v>45670</v>
       </c>
@@ -10135,7 +10135,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8">
       <c r="A49" s="6">
         <v>45671</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8">
       <c r="A50" s="6">
         <v>45671</v>
       </c>
@@ -10187,7 +10187,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8">
       <c r="A51" s="6">
         <v>45671</v>
       </c>
@@ -10213,7 +10213,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8">
       <c r="A52" s="6">
         <v>45671</v>
       </c>
@@ -10239,7 +10239,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8">
       <c r="A53" s="6">
         <v>45671</v>
       </c>
@@ -10265,7 +10265,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8">
       <c r="A54" s="6">
         <v>45671</v>
       </c>
@@ -10291,7 +10291,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8">
       <c r="A55" s="6">
         <v>45672</v>
       </c>
@@ -10317,7 +10317,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8">
       <c r="A56" s="6">
         <v>45672</v>
       </c>
@@ -10343,7 +10343,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8">
       <c r="A57" s="6">
         <v>45672</v>
       </c>
@@ -10369,7 +10369,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8">
       <c r="A58" s="6">
         <v>45672</v>
       </c>
@@ -10395,7 +10395,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8">
       <c r="A59" s="6">
         <v>45672</v>
       </c>
@@ -10421,7 +10421,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8">
       <c r="A60" s="6">
         <v>45672</v>
       </c>
@@ -10447,7 +10447,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8">
       <c r="A61" s="6">
         <v>45673</v>
       </c>
@@ -10473,7 +10473,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8">
       <c r="A62" s="6">
         <v>45673</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8">
       <c r="A63" s="6">
         <v>45673</v>
       </c>
@@ -10525,7 +10525,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8">
       <c r="A64" s="6">
         <v>45673</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8">
       <c r="A65" s="6">
         <v>45674</v>
       </c>
@@ -10577,7 +10577,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8">
       <c r="A66" s="6">
         <v>45674</v>
       </c>
@@ -10603,7 +10603,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8">
       <c r="A67" s="6">
         <v>45674</v>
       </c>
@@ -10629,7 +10629,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8">
       <c r="A68" s="6">
         <v>45674</v>
       </c>
@@ -10655,7 +10655,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8">
       <c r="A69" s="6">
         <v>45675</v>
       </c>
@@ -10681,7 +10681,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8">
       <c r="A70" s="6">
         <v>45675</v>
       </c>
@@ -10707,7 +10707,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8">
       <c r="A71" s="6">
         <v>45675</v>
       </c>
@@ -10733,7 +10733,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8">
       <c r="A72" s="6">
         <v>45675</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8">
       <c r="A73" s="6">
         <v>45677</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8">
       <c r="A74" s="6">
         <v>45677</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8">
       <c r="A75" s="6">
         <v>45677</v>
       </c>
@@ -10837,7 +10837,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8">
       <c r="A76" s="6">
         <v>45677</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8">
       <c r="A77" s="6">
         <v>45678</v>
       </c>
@@ -10889,7 +10889,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8">
       <c r="A78" s="6">
         <v>45678</v>
       </c>
@@ -10915,7 +10915,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8">
       <c r="A79" s="6">
         <v>45678</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8">
       <c r="A80" s="6">
         <v>45678</v>
       </c>
@@ -10967,7 +10967,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8">
       <c r="A81" s="6">
         <v>45679</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8">
       <c r="A82" s="6">
         <v>45679</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8">
       <c r="A83" s="6">
         <v>45679</v>
       </c>
@@ -11045,7 +11045,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8">
       <c r="A84" s="6">
         <v>45679</v>
       </c>
@@ -11071,7 +11071,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8">
       <c r="A85" s="6">
         <v>45679</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8">
       <c r="A86" s="6">
         <v>45680</v>
       </c>
@@ -11123,7 +11123,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8">
       <c r="A87" s="6">
         <v>45680</v>
       </c>
@@ -11149,7 +11149,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8">
       <c r="A88" s="6">
         <v>45680</v>
       </c>
@@ -11175,7 +11175,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8">
       <c r="A89" s="6">
         <v>45681</v>
       </c>
@@ -11201,7 +11201,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8">
       <c r="A90" s="6">
         <v>45688</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8">
       <c r="A91" s="6">
         <v>45691</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8">
       <c r="A92" s="6">
         <v>45691</v>
       </c>
@@ -11279,7 +11279,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8">
       <c r="A93" s="6">
         <v>45692</v>
       </c>
@@ -11305,7 +11305,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8">
       <c r="A94" s="6">
         <v>45692</v>
       </c>
@@ -11331,7 +11331,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8">
       <c r="A95" s="6">
         <v>45693</v>
       </c>
@@ -11357,7 +11357,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8">
       <c r="A96" s="6">
         <v>45693</v>
       </c>
@@ -11383,7 +11383,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8">
       <c r="A97" s="6">
         <v>45693</v>
       </c>
@@ -11409,7 +11409,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8">
       <c r="A98" s="6">
         <v>45695</v>
       </c>
@@ -11435,7 +11435,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8">
       <c r="A99" s="6">
         <v>45695</v>
       </c>
@@ -11461,7 +11461,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8">
       <c r="A100" s="6">
         <v>45699</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8">
       <c r="A101" s="6">
         <v>45699</v>
       </c>
@@ -11513,7 +11513,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8">
       <c r="A102" s="6">
         <v>45699</v>
       </c>
@@ -11539,7 +11539,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8">
       <c r="A103" s="6">
         <v>45700</v>
       </c>
@@ -11565,7 +11565,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8">
       <c r="A104" s="6">
         <v>45700</v>
       </c>
@@ -11591,7 +11591,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8">
       <c r="A105" s="6">
         <v>45700</v>
       </c>
@@ -11617,7 +11617,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8">
       <c r="A106" s="6">
         <v>45700</v>
       </c>
@@ -11643,7 +11643,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8">
       <c r="A107" s="6">
         <v>45700</v>
       </c>
@@ -11669,7 +11669,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8">
       <c r="A108" s="6">
         <v>45701</v>
       </c>
@@ -11695,7 +11695,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8">
       <c r="A109" s="6">
         <v>45701</v>
       </c>
@@ -11721,7 +11721,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8">
       <c r="A110" s="6">
         <v>45701</v>
       </c>
@@ -11747,7 +11747,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8">
       <c r="A111" s="6">
         <v>45701</v>
       </c>
@@ -11773,7 +11773,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8">
       <c r="A112" s="6">
         <v>45702</v>
       </c>
@@ -11799,7 +11799,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8">
       <c r="A113" s="6">
         <v>45703</v>
       </c>
@@ -11825,7 +11825,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8">
       <c r="A114" s="6">
         <v>45705</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8">
       <c r="A115" s="6">
         <v>45706</v>
       </c>
@@ -11877,7 +11877,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8">
       <c r="A116" s="6">
         <v>45706</v>
       </c>
@@ -11903,7 +11903,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8">
       <c r="A117" s="6">
         <v>45707</v>
       </c>
@@ -11929,7 +11929,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8">
       <c r="A118" s="6">
         <v>45707</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8">
       <c r="A119" s="6">
         <v>45707</v>
       </c>
@@ -11981,7 +11981,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8">
       <c r="A120" s="6">
         <v>45707</v>
       </c>
@@ -12007,7 +12007,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8">
       <c r="A121" s="6">
         <v>45708</v>
       </c>
@@ -12033,7 +12033,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8">
       <c r="A122" s="6">
         <v>45708</v>
       </c>
@@ -12059,7 +12059,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8">
       <c r="A123" s="6">
         <v>45708</v>
       </c>
@@ -12085,7 +12085,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8">
       <c r="A124" s="6">
         <v>45708</v>
       </c>
@@ -12111,7 +12111,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8">
       <c r="A125" s="6">
         <v>45708</v>
       </c>
@@ -12137,7 +12137,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8">
       <c r="A126" s="6">
         <v>45708</v>
       </c>
@@ -12163,7 +12163,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8">
       <c r="A127" s="6">
         <v>45709</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8">
       <c r="A128" s="6">
         <v>45709</v>
       </c>
@@ -12215,7 +12215,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8">
       <c r="A129" s="6">
         <v>45709</v>
       </c>
@@ -12241,7 +12241,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8">
       <c r="A130" s="6">
         <v>45710</v>
       </c>
@@ -12267,7 +12267,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8">
       <c r="A131" s="6">
         <v>45710</v>
       </c>
@@ -12293,7 +12293,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8">
       <c r="A132" s="6">
         <v>45710</v>
       </c>
@@ -12319,7 +12319,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8">
       <c r="A133" s="6">
         <v>45712</v>
       </c>
@@ -12345,7 +12345,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8">
       <c r="A134" s="6">
         <v>45712</v>
       </c>
@@ -12371,7 +12371,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8">
       <c r="A135" s="6">
         <v>45712</v>
       </c>
@@ -12397,7 +12397,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8">
       <c r="A136" s="6">
         <v>45712</v>
       </c>
@@ -12423,7 +12423,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8">
       <c r="A137" s="6">
         <v>45712</v>
       </c>
@@ -12449,7 +12449,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8">
       <c r="A138" s="6">
         <v>45713</v>
       </c>
@@ -12475,7 +12475,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8">
       <c r="A139" s="6">
         <v>45713</v>
       </c>
@@ -12501,7 +12501,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8">
       <c r="A140" s="6">
         <v>45713</v>
       </c>
@@ -12527,7 +12527,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8">
       <c r="A141" s="6">
         <v>45713</v>
       </c>
@@ -12553,7 +12553,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8">
       <c r="A142" s="6">
         <v>45713</v>
       </c>
@@ -12579,7 +12579,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8">
       <c r="A143" s="6">
         <v>45714</v>
       </c>
@@ -12605,7 +12605,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8">
       <c r="A144" s="6">
         <v>45714</v>
       </c>
@@ -12631,7 +12631,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8">
       <c r="A145" s="6">
         <v>45714</v>
       </c>
@@ -12657,7 +12657,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8">
       <c r="A146" s="6">
         <v>45715</v>
       </c>
@@ -12683,7 +12683,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8">
       <c r="A147" s="6">
         <v>45715</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8">
       <c r="A148" s="6">
         <v>45715</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8">
       <c r="A149" s="6">
         <v>45716</v>
       </c>
@@ -12761,7 +12761,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8">
       <c r="A150" s="6">
         <v>45716</v>
       </c>
@@ -12787,7 +12787,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8">
       <c r="A151" s="6">
         <v>45716</v>
       </c>
@@ -12813,7 +12813,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8">
       <c r="A152" s="6">
         <v>45716</v>
       </c>
@@ -12839,7 +12839,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8">
       <c r="A153" s="6">
         <v>45721</v>
       </c>
@@ -12865,7 +12865,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8">
       <c r="A154" s="6">
         <v>45722</v>
       </c>
@@ -12891,7 +12891,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8">
       <c r="A155" s="6">
         <v>45726</v>
       </c>
@@ -12917,7 +12917,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8">
       <c r="A156" s="6">
         <v>45740</v>
       </c>
@@ -12943,7 +12943,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8">
       <c r="A157" s="6">
         <v>45741</v>
       </c>
@@ -12969,7 +12969,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8">
       <c r="A158" s="6">
         <v>45741</v>
       </c>
@@ -12995,7 +12995,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8">
       <c r="A159" s="6">
         <v>45743</v>
       </c>
@@ -13021,7 +13021,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8">
       <c r="A160" s="6">
         <v>45744</v>
       </c>
@@ -13047,7 +13047,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8">
       <c r="A161" s="6">
         <v>45748</v>
       </c>
@@ -13073,7 +13073,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8">
       <c r="A162" s="6">
         <v>45757</v>
       </c>
@@ -13099,7 +13099,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8">
       <c r="A163" s="6">
         <v>45758</v>
       </c>
@@ -13125,7 +13125,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8">
       <c r="A164" s="6">
         <v>45770</v>
       </c>
@@ -13151,7 +13151,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8">
       <c r="A165" s="6">
         <v>45779</v>
       </c>
@@ -13177,7 +13177,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8">
       <c r="A166" s="6">
         <v>45784</v>
       </c>
@@ -13203,7 +13203,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8">
       <c r="A167" s="6">
         <v>45799</v>
       </c>
@@ -13229,7 +13229,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8">
       <c r="A168" s="6">
         <v>45808</v>
       </c>
@@ -13255,7 +13255,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8">
       <c r="A169" s="6">
         <v>45812</v>
       </c>
@@ -13281,7 +13281,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8">
       <c r="A170" s="6">
         <v>45812</v>
       </c>
@@ -13307,7 +13307,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8">
       <c r="A171" s="6">
         <v>45813</v>
       </c>
@@ -13333,7 +13333,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8">
       <c r="A172" s="6">
         <v>45813</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8">
       <c r="A173" s="6">
         <v>45814</v>
       </c>
@@ -13385,7 +13385,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8">
       <c r="A174" s="6">
         <v>45815</v>
       </c>
@@ -13411,7 +13411,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8">
       <c r="A175" s="6">
         <v>45815</v>
       </c>
@@ -13437,7 +13437,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8">
       <c r="A176" s="6">
         <v>45817</v>
       </c>
@@ -13463,7 +13463,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8">
       <c r="A177" s="6">
         <v>45818</v>
       </c>
@@ -13489,7 +13489,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8">
       <c r="A178" s="6">
         <v>45818</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8">
       <c r="A179" s="6">
         <v>45819</v>
       </c>
@@ -13541,7 +13541,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8">
       <c r="A180" s="6">
         <v>45819</v>
       </c>
@@ -13567,7 +13567,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8">
       <c r="A181" s="6">
         <v>45820</v>
       </c>
@@ -13593,7 +13593,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8">
       <c r="A182" s="6">
         <v>45820</v>
       </c>
@@ -13619,7 +13619,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8">
       <c r="A183" s="6">
         <v>45822</v>
       </c>
@@ -13645,7 +13645,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8">
       <c r="A184" s="6">
         <v>45822</v>
       </c>
@@ -13671,7 +13671,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8">
       <c r="A185" s="6">
         <v>45824</v>
       </c>
@@ -13697,7 +13697,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8">
       <c r="A186" s="6">
         <v>45824</v>
       </c>
@@ -13723,7 +13723,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8">
       <c r="A187" s="6">
         <v>45825</v>
       </c>
@@ -13749,7 +13749,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8">
       <c r="A188" s="6">
         <v>45825</v>
       </c>
@@ -13775,7 +13775,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8">
       <c r="A189" s="6">
         <v>45826</v>
       </c>
@@ -13801,7 +13801,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8">
       <c r="A190" s="6">
         <v>45826</v>
       </c>
@@ -13827,7 +13827,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8">
       <c r="A191" s="6">
         <v>45827</v>
       </c>
@@ -13853,7 +13853,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8">
       <c r="A192" s="6">
         <v>45827</v>
       </c>
@@ -13879,7 +13879,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8">
       <c r="A193" s="6">
         <v>45828</v>
       </c>
@@ -13905,7 +13905,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8">
       <c r="A194" s="6">
         <v>45828</v>
       </c>
@@ -13931,7 +13931,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8">
       <c r="A195" s="6">
         <v>45829</v>
       </c>
@@ -13957,7 +13957,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8">
       <c r="A196" s="6">
         <v>45829</v>
       </c>
@@ -13983,7 +13983,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8">
       <c r="A197" s="6">
         <v>45830</v>
       </c>
@@ -14009,7 +14009,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8">
       <c r="A198" s="6">
         <v>45831</v>
       </c>
@@ -14035,7 +14035,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8">
       <c r="A199" s="6">
         <v>45831</v>
       </c>
@@ -14061,7 +14061,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8">
       <c r="A200" s="6">
         <v>45832</v>
       </c>
@@ -14087,7 +14087,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8">
       <c r="A201" s="6">
         <v>45832</v>
       </c>
@@ -14113,7 +14113,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8">
       <c r="A202" s="6">
         <v>45833</v>
       </c>
@@ -14139,7 +14139,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8">
       <c r="A203" s="6">
         <v>45834</v>
       </c>
@@ -14165,7 +14165,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8">
       <c r="A204" s="6">
         <v>45835</v>
       </c>
@@ -14191,7 +14191,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8">
       <c r="A205" s="6">
         <v>45835</v>
       </c>
@@ -14217,7 +14217,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8">
       <c r="A206" s="6">
         <v>45836</v>
       </c>
@@ -14243,7 +14243,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8">
       <c r="A207" s="6">
         <v>45838</v>
       </c>
@@ -14269,7 +14269,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8">
       <c r="A208" s="6">
         <v>45838</v>
       </c>
@@ -14295,7 +14295,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8">
       <c r="A209" s="6">
         <v>45839</v>
       </c>
@@ -14321,7 +14321,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8">
       <c r="A210" s="6">
         <v>45839</v>
       </c>
@@ -14347,7 +14347,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8">
       <c r="A211" s="6">
         <v>45840</v>
       </c>
@@ -14373,7 +14373,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8">
       <c r="A212" s="6">
         <v>45840</v>
       </c>
@@ -14399,7 +14399,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8">
       <c r="A213" s="6">
         <v>45841</v>
       </c>
@@ -14425,7 +14425,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8">
       <c r="A214" s="6">
         <v>45841</v>
       </c>
@@ -14451,7 +14451,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8">
       <c r="A215" s="6">
         <v>45842</v>
       </c>
@@ -14477,7 +14477,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8">
       <c r="A216" s="6">
         <v>45842</v>
       </c>
@@ -14503,7 +14503,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8">
       <c r="A217" s="6">
         <v>45843</v>
       </c>
@@ -14529,7 +14529,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8">
       <c r="A218" s="6">
         <v>45843</v>
       </c>
@@ -14555,7 +14555,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8">
       <c r="A219" s="6">
         <v>45845</v>
       </c>
@@ -14581,7 +14581,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8">
       <c r="A220" s="6">
         <v>45845</v>
       </c>
@@ -14607,7 +14607,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8">
       <c r="A221" s="6">
         <v>45846</v>
       </c>
@@ -14633,7 +14633,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8">
       <c r="A222" s="6">
         <v>45846</v>
       </c>
@@ -14659,7 +14659,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8">
       <c r="A223" s="6">
         <v>45847</v>
       </c>
@@ -14685,7 +14685,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8">
       <c r="A224" s="6">
         <v>45847</v>
       </c>
@@ -14711,7 +14711,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8">
       <c r="A225" s="6">
         <v>45848</v>
       </c>
@@ -14737,7 +14737,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8">
       <c r="A226" s="6">
         <v>45848</v>
       </c>
@@ -14763,7 +14763,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8">
       <c r="A227" s="6">
         <v>45849</v>
       </c>
@@ -14789,7 +14789,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8">
       <c r="A228" s="6">
         <v>45849</v>
       </c>
@@ -14815,7 +14815,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8">
       <c r="A229" s="6">
         <v>45850</v>
       </c>
@@ -14841,7 +14841,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8">
       <c r="A230" s="6">
         <v>45850</v>
       </c>
@@ -14867,7 +14867,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8">
       <c r="A231" s="6">
         <v>45851</v>
       </c>
@@ -14893,7 +14893,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8">
       <c r="A232" s="6">
         <v>45852</v>
       </c>
@@ -14919,7 +14919,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8">
       <c r="A233" s="6">
         <v>45852</v>
       </c>
@@ -14945,7 +14945,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8">
       <c r="A234" s="6">
         <v>45853</v>
       </c>
@@ -14971,7 +14971,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8">
       <c r="A235" s="6">
         <v>45854</v>
       </c>
@@ -14997,7 +14997,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8">
       <c r="A236" s="6">
         <v>45854</v>
       </c>
@@ -15023,7 +15023,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8">
       <c r="A237" s="6">
         <v>45855</v>
       </c>
@@ -15049,7 +15049,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8">
       <c r="A238" s="6">
         <v>45855</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8">
       <c r="A239" s="6">
         <v>45856</v>
       </c>
@@ -15101,7 +15101,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8">
       <c r="A240" s="6">
         <v>45856</v>
       </c>
@@ -15127,7 +15127,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8">
       <c r="A241" s="6">
         <v>45857</v>
       </c>
@@ -15153,7 +15153,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8">
       <c r="A242" s="6">
         <v>45857</v>
       </c>
@@ -15179,7 +15179,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8">
       <c r="A243" s="6">
         <v>45859</v>
       </c>
@@ -15205,7 +15205,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8">
       <c r="A244" s="6">
         <v>45859</v>
       </c>
@@ -15231,7 +15231,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8">
       <c r="A245" s="6">
         <v>45860</v>
       </c>
@@ -15257,7 +15257,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8">
       <c r="A246" s="6">
         <v>45860</v>
       </c>
@@ -15283,7 +15283,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8">
       <c r="A247" s="6">
         <v>45861</v>
       </c>
@@ -15309,7 +15309,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8">
       <c r="A248" s="6">
         <v>45861</v>
       </c>
@@ -15335,7 +15335,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8">
       <c r="A249" s="6">
         <v>45862</v>
       </c>
@@ -15361,7 +15361,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8">
       <c r="A250" s="6">
         <v>45862</v>
       </c>
@@ -15387,7 +15387,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8">
       <c r="A251" s="6">
         <v>45863</v>
       </c>
@@ -15413,7 +15413,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8">
       <c r="A252" s="6">
         <v>45863</v>
       </c>
@@ -15439,7 +15439,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8">
       <c r="A253" s="6">
         <v>45864</v>
       </c>
@@ -15465,7 +15465,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8">
       <c r="A254" s="6">
         <v>45866</v>
       </c>
@@ -15491,7 +15491,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8">
       <c r="A255" s="6">
         <v>45866</v>
       </c>
@@ -15517,7 +15517,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8">
       <c r="A256" s="6">
         <v>45867</v>
       </c>
@@ -15543,7 +15543,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9">
       <c r="A257" s="6">
         <v>45868</v>
       </c>
@@ -15569,7 +15569,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9">
       <c r="A258" s="6">
         <v>45868</v>
       </c>
@@ -15595,7 +15595,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9">
       <c r="A259" s="6">
         <v>45869</v>
       </c>
@@ -15621,7 +15621,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9">
       <c r="A260" s="6">
         <v>45869</v>
       </c>
@@ -15647,7 +15647,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9">
       <c r="A261" s="6">
         <v>45870</v>
       </c>
@@ -15673,7 +15673,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9">
       <c r="A262" s="6">
         <v>45870</v>
       </c>
@@ -15699,7 +15699,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9">
       <c r="A263" s="6">
         <v>45870</v>
       </c>
@@ -15725,7 +15725,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9">
       <c r="A264" s="6">
         <v>45871</v>
       </c>
@@ -15751,7 +15751,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9">
       <c r="A265" s="6">
         <v>45871</v>
       </c>
@@ -15777,7 +15777,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9">
       <c r="A266" s="6">
         <v>45871</v>
       </c>
@@ -15803,7 +15803,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9">
       <c r="A267" s="6">
         <v>45873</v>
       </c>
@@ -15829,7 +15829,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9">
       <c r="A268" s="6">
         <v>45873</v>
       </c>
@@ -15855,7 +15855,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9">
       <c r="A269" s="6">
         <v>45873</v>
       </c>
@@ -15881,7 +15881,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9">
       <c r="A270" s="6">
         <v>45873</v>
       </c>
@@ -15907,7 +15907,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9">
       <c r="A271" s="6">
         <v>45874</v>
       </c>
@@ -15936,7 +15936,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9">
       <c r="A272" s="6">
         <v>45874</v>
       </c>
@@ -15965,7 +15965,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9">
       <c r="A273" s="6">
         <v>45874</v>
       </c>
@@ -15991,7 +15991,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9">
       <c r="A274" s="6">
         <v>45874</v>
       </c>
@@ -16017,7 +16017,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9">
       <c r="A275" s="6">
         <v>45875</v>
       </c>
@@ -16043,7 +16043,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9">
       <c r="A276" s="6">
         <v>45875</v>
       </c>
@@ -16069,7 +16069,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9">
       <c r="A277" s="6">
         <v>45875</v>
       </c>
@@ -16095,7 +16095,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9">
       <c r="A278" s="6">
         <v>45875</v>
       </c>
@@ -16121,7 +16121,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9">
       <c r="A279" s="6">
         <v>45876</v>
       </c>
@@ -16147,7 +16147,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9">
       <c r="A280" s="6">
         <v>45876</v>
       </c>
@@ -16173,7 +16173,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9">
       <c r="A281" s="6">
         <v>45876</v>
       </c>
@@ -16199,7 +16199,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9">
       <c r="A282" s="6">
         <v>45876</v>
       </c>
@@ -16225,7 +16225,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9">
       <c r="A283" s="6">
         <v>45877</v>
       </c>
@@ -16251,7 +16251,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9">
       <c r="A284" s="6">
         <v>45877</v>
       </c>
@@ -16277,7 +16277,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9">
       <c r="A285" s="6">
         <v>45877</v>
       </c>
@@ -16303,7 +16303,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9">
       <c r="A286" s="6">
         <v>45877</v>
       </c>
@@ -16329,7 +16329,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9">
       <c r="A287" s="6">
         <v>45878</v>
       </c>
@@ -16358,7 +16358,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9">
       <c r="A288" s="6">
         <v>45878</v>
       </c>
@@ -16384,7 +16384,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9">
       <c r="A289" s="6">
         <v>45878</v>
       </c>
@@ -16410,7 +16410,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9">
       <c r="A290" s="6">
         <v>45878</v>
       </c>
@@ -16436,7 +16436,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9">
       <c r="A291" s="6">
         <v>45880</v>
       </c>
@@ -16462,7 +16462,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9">
       <c r="A292" s="6">
         <v>45880</v>
       </c>
@@ -16488,7 +16488,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9">
       <c r="A293" s="6">
         <v>45880</v>
       </c>
@@ -16514,7 +16514,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9">
       <c r="A294" s="6">
         <v>45881</v>
       </c>
@@ -16540,7 +16540,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9">
       <c r="A295" s="6">
         <v>45881</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9">
       <c r="A296" s="6">
         <v>45881</v>
       </c>
@@ -16592,7 +16592,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9">
       <c r="A297" s="6">
         <v>45881</v>
       </c>
@@ -16618,7 +16618,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9">
       <c r="A298" s="6">
         <v>45881</v>
       </c>
@@ -16644,7 +16644,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9">
       <c r="A299" s="6">
         <v>45882</v>
       </c>
@@ -16670,7 +16670,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9">
       <c r="A300" s="6">
         <v>45882</v>
       </c>
@@ -16699,7 +16699,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9">
       <c r="A301" s="6">
         <v>45882</v>
       </c>
@@ -16728,7 +16728,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9">
       <c r="A302" s="6">
         <v>45882</v>
       </c>
@@ -16754,7 +16754,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9">
       <c r="A303" s="6">
         <v>45882</v>
       </c>
@@ -16780,7 +16780,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9">
       <c r="A304" s="6">
         <v>45883</v>
       </c>
@@ -16809,7 +16809,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9">
       <c r="A305" s="6">
         <v>45883</v>
       </c>
@@ -16835,7 +16835,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9">
       <c r="A306" s="6">
         <v>45883</v>
       </c>
@@ -16861,7 +16861,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9">
       <c r="A307" s="6">
         <v>45883</v>
       </c>
@@ -16887,7 +16887,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9">
       <c r="A308" s="6">
         <v>45883</v>
       </c>
@@ -16913,7 +16913,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9">
       <c r="A309" s="6">
         <v>45884</v>
       </c>
@@ -16939,7 +16939,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9">
       <c r="A310" s="6">
         <v>45884</v>
       </c>
@@ -16965,7 +16965,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9">
       <c r="A311" s="6">
         <v>45884</v>
       </c>
@@ -16991,7 +16991,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9">
       <c r="A312" s="6">
         <v>45885</v>
       </c>
@@ -17020,7 +17020,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9">
       <c r="A313" s="6">
         <v>45885</v>
       </c>
@@ -17046,7 +17046,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9">
       <c r="A314" s="6">
         <v>45885</v>
       </c>
@@ -17075,7 +17075,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9">
       <c r="A315" s="6">
         <v>45885</v>
       </c>
@@ -17104,7 +17104,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9">
       <c r="A316" s="6">
         <v>45887</v>
       </c>
@@ -17130,7 +17130,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9">
       <c r="A317" s="6">
         <v>45887</v>
       </c>
@@ -17156,7 +17156,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9">
       <c r="A318" s="6">
         <v>45887</v>
       </c>
@@ -17182,7 +17182,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9">
       <c r="A319" s="6">
         <v>45887</v>
       </c>
@@ -17208,7 +17208,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9">
       <c r="A320" s="6">
         <v>45887</v>
       </c>
@@ -17234,7 +17234,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9">
       <c r="A321" s="6">
         <v>45888</v>
       </c>
@@ -17260,7 +17260,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9">
       <c r="A322" s="6">
         <v>45888</v>
       </c>
@@ -17286,7 +17286,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9">
       <c r="A323" s="6">
         <v>45888</v>
       </c>
@@ -17312,7 +17312,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9">
       <c r="A324" s="6">
         <v>45888</v>
       </c>
@@ -17338,7 +17338,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9">
       <c r="A325" s="6">
         <v>45888</v>
       </c>
@@ -17364,7 +17364,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9">
       <c r="A326" s="6">
         <v>45889</v>
       </c>
@@ -17393,7 +17393,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9">
       <c r="A327" s="6">
         <v>45889</v>
       </c>
@@ -17419,7 +17419,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9">
       <c r="A328" s="6">
         <v>45889</v>
       </c>
@@ -17445,7 +17445,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9">
       <c r="A329" s="6">
         <v>45889</v>
       </c>
@@ -17471,7 +17471,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9">
       <c r="A330" s="6">
         <v>45889</v>
       </c>
@@ -17497,7 +17497,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9">
       <c r="A331" s="6">
         <v>45890</v>
       </c>
@@ -17526,7 +17526,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9">
       <c r="A332" s="6">
         <v>45890</v>
       </c>
@@ -17552,7 +17552,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9">
       <c r="A333" s="6">
         <v>45890</v>
       </c>
@@ -17578,7 +17578,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9">
       <c r="A334" s="6">
         <v>45890</v>
       </c>
@@ -17604,7 +17604,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9">
       <c r="A335" s="6">
         <v>45891</v>
       </c>
@@ -17630,7 +17630,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9">
       <c r="A336" s="6">
         <v>45891</v>
       </c>
@@ -17656,7 +17656,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9">
       <c r="A337" s="6">
         <v>45891</v>
       </c>
@@ -17682,7 +17682,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9">
       <c r="A338" s="6">
         <v>45891</v>
       </c>
@@ -17708,7 +17708,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9">
       <c r="A339" s="6">
         <v>45891</v>
       </c>
@@ -17734,7 +17734,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9">
       <c r="A340" s="6">
         <v>45892</v>
       </c>
@@ -17763,7 +17763,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9">
       <c r="A341" s="6">
         <v>45892</v>
       </c>
@@ -17792,7 +17792,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9">
       <c r="A342" s="6">
         <v>45892</v>
       </c>
@@ -17821,7 +17821,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9">
       <c r="A343" s="6">
         <v>45892</v>
       </c>
@@ -17850,7 +17850,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9">
       <c r="A344" s="6">
         <v>45892</v>
       </c>
@@ -17879,7 +17879,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9">
       <c r="A345" s="6">
         <v>45894</v>
       </c>
@@ -17908,7 +17908,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9">
       <c r="A346" s="6">
         <v>45894</v>
       </c>
@@ -17937,7 +17937,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9">
       <c r="A347" s="6">
         <v>45895</v>
       </c>
@@ -17966,7 +17966,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9">
       <c r="A348" s="6">
         <v>45895</v>
       </c>
@@ -17995,7 +17995,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9">
       <c r="A349" s="6">
         <v>45895</v>
       </c>
@@ -18024,7 +18024,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9">
       <c r="A350" s="6">
         <v>45896</v>
       </c>
@@ -18053,7 +18053,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9">
       <c r="A351" s="6">
         <v>45896</v>
       </c>
@@ -18082,7 +18082,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9">
       <c r="A352" s="6">
         <v>45896</v>
       </c>
@@ -18111,7 +18111,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9">
       <c r="A353" s="6">
         <v>45897</v>
       </c>
@@ -18140,7 +18140,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9">
       <c r="A354" s="6">
         <v>45897</v>
       </c>
@@ -18169,7 +18169,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9">
       <c r="A355" s="6">
         <v>45897</v>
       </c>
@@ -18198,7 +18198,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9">
       <c r="A356" s="6">
         <v>45898</v>
       </c>
@@ -18227,7 +18227,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9">
       <c r="A357" s="6">
         <v>45898</v>
       </c>
@@ -18256,7 +18256,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9">
       <c r="A358" s="6">
         <v>45898</v>
       </c>
@@ -18285,7 +18285,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9">
       <c r="A359" s="6">
         <v>45898</v>
       </c>
@@ -18314,7 +18314,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9">
       <c r="A360" s="6">
         <v>45899</v>
       </c>
@@ -18343,7 +18343,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9">
       <c r="A361" s="6">
         <v>45899</v>
       </c>
@@ -18372,7 +18372,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9">
       <c r="A362" s="6">
         <v>45899</v>
       </c>
@@ -18401,7 +18401,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9">
       <c r="A363" s="6">
         <v>45899</v>
       </c>
@@ -18430,7 +18430,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9">
       <c r="A364" s="6">
         <v>45900</v>
       </c>
@@ -18459,7 +18459,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9">
       <c r="A365" s="6">
         <v>45901</v>
       </c>
@@ -18485,7 +18485,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9">
       <c r="A366" s="6">
         <v>45901</v>
       </c>
@@ -18511,7 +18511,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9">
       <c r="A367" s="6">
         <v>45901</v>
       </c>
@@ -18540,7 +18540,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9">
       <c r="A368" s="6">
         <v>45901</v>
       </c>
@@ -18569,7 +18569,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:9">
       <c r="A369" s="6">
         <v>45902</v>
       </c>
@@ -18598,7 +18598,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:9">
       <c r="A370" s="6">
         <v>45902</v>
       </c>
@@ -18627,7 +18627,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:9">
       <c r="A371" s="6">
         <v>45902</v>
       </c>
@@ -18656,7 +18656,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:9">
       <c r="A372" s="6">
         <v>45902</v>
       </c>
@@ -18685,7 +18685,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:9">
       <c r="A373" s="6">
         <v>45902</v>
       </c>
@@ -18714,7 +18714,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:9">
       <c r="A374" s="6">
         <v>45903</v>
       </c>
@@ -18743,7 +18743,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:9">
       <c r="A375" s="6">
         <v>45903</v>
       </c>
@@ -18772,7 +18772,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:9">
       <c r="A376" s="6">
         <v>45903</v>
       </c>
@@ -18801,7 +18801,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:9">
       <c r="A377" s="6">
         <v>45903</v>
       </c>
@@ -18830,7 +18830,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:9">
       <c r="A378" s="6">
         <v>45903</v>
       </c>
@@ -18859,7 +18859,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:9">
       <c r="A379" s="6">
         <v>45904</v>
       </c>
@@ -18888,7 +18888,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:9">
       <c r="A380" s="6">
         <v>45904</v>
       </c>
@@ -18914,7 +18914,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:9">
       <c r="A381" s="6">
         <v>45904</v>
       </c>
@@ -18940,7 +18940,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:9">
       <c r="A382" s="6">
         <v>45904</v>
       </c>
@@ -18969,7 +18969,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:9">
       <c r="A383" s="6">
         <v>45904</v>
       </c>
@@ -18998,7 +18998,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:9">
       <c r="A384" s="6">
         <v>45905</v>
       </c>
@@ -19027,7 +19027,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:9">
       <c r="A385" s="6">
         <v>45905</v>
       </c>
@@ -19056,7 +19056,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:9">
       <c r="A386" s="6">
         <v>45905</v>
       </c>
@@ -19085,7 +19085,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:9">
       <c r="A387" s="6">
         <v>45905</v>
       </c>
@@ -19111,7 +19111,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:9">
       <c r="A388" s="6">
         <v>45905</v>
       </c>
@@ -19137,7 +19137,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:9">
       <c r="A389" s="6">
         <v>45905</v>
       </c>
@@ -19163,7 +19163,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:9">
       <c r="A390" s="6">
         <v>45905</v>
       </c>
@@ -19189,7 +19189,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:9">
       <c r="A391" s="6">
         <v>45906</v>
       </c>
@@ -19218,7 +19218,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:9">
       <c r="A392" s="6">
         <v>45906</v>
       </c>
@@ -19247,7 +19247,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:9">
       <c r="A393" s="6">
         <v>45906</v>
       </c>
@@ -19273,7 +19273,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:9">
       <c r="A394" s="6">
         <v>45906</v>
       </c>
@@ -19302,7 +19302,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:9">
       <c r="A395" s="6">
         <v>45906</v>
       </c>
@@ -19331,7 +19331,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:9">
       <c r="A396" s="6">
         <v>45907</v>
       </c>
@@ -19360,7 +19360,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:9">
       <c r="A397" s="6">
         <v>45907</v>
       </c>
@@ -19389,7 +19389,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:9">
       <c r="A398" s="6">
         <v>45908</v>
       </c>
@@ -19415,7 +19415,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:9">
       <c r="A399" s="6">
         <v>45908</v>
       </c>
@@ -19444,7 +19444,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:9">
       <c r="A400" s="6">
         <v>45908</v>
       </c>
@@ -19473,7 +19473,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:9">
       <c r="A401" s="6">
         <v>45908</v>
       </c>
@@ -19502,7 +19502,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:9">
       <c r="A402" s="6">
         <v>45909</v>
       </c>
@@ -19531,7 +19531,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:9">
       <c r="A403" s="6">
         <v>45909</v>
       </c>
@@ -19560,7 +19560,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:9">
       <c r="A404" s="6">
         <v>45909</v>
       </c>
@@ -19589,7 +19589,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:9">
       <c r="A405" s="6">
         <v>45909</v>
       </c>
@@ -19618,7 +19618,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:9">
       <c r="A406" s="6">
         <v>45909</v>
       </c>
@@ -19647,7 +19647,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:9">
       <c r="A407" s="6">
         <v>45910</v>
       </c>
@@ -19673,7 +19673,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:9">
       <c r="A408" s="6">
         <v>45910</v>
       </c>
@@ -19702,7 +19702,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:9">
       <c r="A409" s="6">
         <v>45910</v>
       </c>
@@ -19731,7 +19731,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:9">
       <c r="A410" s="6">
         <v>45910</v>
       </c>
@@ -19757,7 +19757,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:9">
       <c r="A411" s="6">
         <v>45911</v>
       </c>
@@ -19786,7 +19786,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:9">
       <c r="A412" s="6">
         <v>45911</v>
       </c>
@@ -19812,7 +19812,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:9">
       <c r="A413" s="6">
         <v>45911</v>
       </c>
@@ -19841,7 +19841,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:9">
       <c r="A414" s="6">
         <v>45912</v>
       </c>
@@ -19870,7 +19870,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:9">
       <c r="A415" s="6">
         <v>45912</v>
       </c>
@@ -19896,7 +19896,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:9">
       <c r="A416" s="6">
         <v>45912</v>
       </c>
@@ -19922,7 +19922,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:9">
       <c r="A417" s="6">
         <v>45913</v>
       </c>
@@ -19951,7 +19951,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:9">
       <c r="A418" s="6">
         <v>45913</v>
       </c>
@@ -19980,7 +19980,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:9">
       <c r="A419" s="6">
         <v>45913</v>
       </c>
@@ -20009,7 +20009,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:9">
       <c r="A420" s="6">
         <v>45915</v>
       </c>
@@ -20035,7 +20035,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:9">
       <c r="A421" s="6">
         <v>45915</v>
       </c>
@@ -20061,7 +20061,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:9">
       <c r="A422" s="6">
         <v>45916</v>
       </c>
@@ -20090,7 +20090,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:9">
       <c r="A423" s="6">
         <v>45916</v>
       </c>
@@ -20119,7 +20119,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:9">
       <c r="A424" s="6">
         <v>45916</v>
       </c>
@@ -20148,7 +20148,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:9">
       <c r="A425" s="6">
         <v>45917</v>
       </c>
@@ -20177,7 +20177,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:9">
       <c r="A426" s="6">
         <v>45917</v>
       </c>
@@ -20203,7 +20203,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:9">
       <c r="A427" s="6">
         <v>45917</v>
       </c>
@@ -20229,7 +20229,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:9">
       <c r="A428" s="6">
         <v>45918</v>
       </c>
@@ -20255,7 +20255,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:9">
       <c r="A429" s="6">
         <v>45918</v>
       </c>
@@ -20281,7 +20281,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:9">
       <c r="A430" s="6">
         <v>45918</v>
       </c>
@@ -20307,7 +20307,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:9">
       <c r="A431" s="6">
         <v>45919</v>
       </c>
@@ -20336,7 +20336,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:9">
       <c r="A432" s="6">
         <v>45919</v>
       </c>
@@ -20362,7 +20362,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:9">
       <c r="A433" s="6">
         <v>45919</v>
       </c>
@@ -20388,7 +20388,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:9">
       <c r="A434" s="6">
         <v>45919</v>
       </c>
@@ -20414,7 +20414,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:9">
       <c r="A435" s="6">
         <v>45920</v>
       </c>
@@ -20443,7 +20443,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:9">
       <c r="A436" s="6">
         <v>45920</v>
       </c>
@@ -20472,7 +20472,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:9">
       <c r="A437" s="6">
         <v>45920</v>
       </c>
@@ -20501,7 +20501,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:9">
       <c r="A438" s="6">
         <v>45922</v>
       </c>
@@ -20530,7 +20530,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:9">
       <c r="A439" s="6">
         <v>45922</v>
       </c>
@@ -20559,7 +20559,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:9">
       <c r="A440" s="6">
         <v>45922</v>
       </c>
@@ -20588,7 +20588,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:9">
       <c r="A441" s="6">
         <v>45922</v>
       </c>
@@ -20617,7 +20617,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:9">
       <c r="A442" s="6">
         <v>45922</v>
       </c>
@@ -20646,7 +20646,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:9">
       <c r="A443" s="6">
         <v>45923</v>
       </c>
@@ -20672,7 +20672,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:9">
       <c r="A444" s="6">
         <v>45923</v>
       </c>
@@ -20698,7 +20698,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:9">
       <c r="A445" s="6">
         <v>45923</v>
       </c>
@@ -20727,7 +20727,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:9">
       <c r="A446" s="6">
         <v>45924</v>
       </c>
@@ -20753,7 +20753,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:9">
       <c r="A447" s="6">
         <v>45924</v>
       </c>
@@ -20779,7 +20779,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:9">
       <c r="A448" s="6">
         <v>45924</v>
       </c>
@@ -20805,7 +20805,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:8">
       <c r="A449" s="6">
         <v>45925</v>
       </c>
@@ -20831,7 +20831,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:8">
       <c r="A450" s="6">
         <v>45925</v>
       </c>
